--- a/Result/profitability/2337.xlsx
+++ b/Result/profitability/2337.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.20625</v>
+        <v>0.3025</v>
       </c>
       <c r="N2" t="n">
-        <v>24.2875</v>
+        <v>28.7225</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.15125</v>
+        <v>0.4425</v>
       </c>
       <c r="N3" t="n">
-        <v>25.5325</v>
+        <v>31.94125</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.68</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03875000000000002</v>
+        <v>0.5862499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>29.14875</v>
+        <v>34.98875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.13</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>32.2325</v>
+        <v>38.32875</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.24125</v>
+        <v>0.78875</v>
       </c>
       <c r="N6" t="n">
-        <v>34.835</v>
+        <v>41.195</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.31</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3387500000000001</v>
+        <v>0.8475</v>
       </c>
       <c r="N7" t="n">
-        <v>38.1575</v>
+        <v>43.18875</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,13 +1391,13 @@
         <v>0.7</v>
       </c>
       <c r="M8" t="n">
-        <v>0.44625</v>
+        <v>0.8225</v>
       </c>
       <c r="N8" t="n">
-        <v>40.9225</v>
+        <v>43.875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1406,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.40375</v>
+        <v>0.4037499999999999</v>
       </c>
       <c r="N9" t="n">
         <v>41.5125</v>
@@ -1645,7 +1645,7 @@
         <v>0.49</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4350000000000001</v>
+        <v>0.4349999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>42.38375</v>
@@ -1775,7 +1775,7 @@
         <v>0.485</v>
       </c>
       <c r="N11" t="n">
-        <v>43.9125</v>
+        <v>43.91249999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.83</v>
       </c>
       <c r="M12" t="n">
-        <v>0.50375</v>
+        <v>0.5037499999999999</v>
       </c>
       <c r="N12" t="n">
         <v>45.895</v>
@@ -2026,10 +2026,10 @@
         <v>0.34</v>
       </c>
       <c r="M13" t="n">
-        <v>0.51375</v>
+        <v>0.5137499999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>47.3975</v>
+        <v>47.39749999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>19125</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6805</v>
+      </c>
+      <c r="E75" t="n">
+        <v>12320</v>
+      </c>
+      <c r="F75" t="n">
+        <v>64.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8968</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>46.89%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>232</v>
+      </c>
+      <c r="J75" t="n">
+        <v>9200</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7732</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.29625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.344444444444444</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5789215686274511</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-6.666666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>3.11629392971246</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
